--- a/planilla-productos-gatecomex.xlsx
+++ b/planilla-productos-gatecomex.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="100">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -68,19 +68,22 @@
     <t xml:space="preserve">Gres Ceramicos</t>
   </si>
   <si>
-    <t xml:space="preserve">Concret Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concreto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68x68 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satinado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interior / Exterior</t>
+    <t xml:space="preserve">CONCRET GRAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68X68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SATINADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interior- Exterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,5mm espesor</t>
   </si>
   <si>
     <t xml:space="preserve">CONCRET GRAY  (1).jpg</t>
@@ -95,10 +98,10 @@
     <t xml:space="preserve">p002</t>
   </si>
   <si>
-    <t xml:space="preserve">Doha Plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrara</t>
+    <t xml:space="preserve">DOHA PLUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARRARA</t>
   </si>
   <si>
     <t xml:space="preserve">DOHA PLUS  (1).jpg</t>
@@ -113,10 +116,10 @@
     <t xml:space="preserve">p003</t>
   </si>
   <si>
-    <t xml:space="preserve">Avorio Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano</t>
+    <t xml:space="preserve">AVORIO GRAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANO</t>
   </si>
   <si>
     <t xml:space="preserve">AVORIO GRAY (1).jpg</t>
@@ -131,7 +134,7 @@
     <t xml:space="preserve">p004</t>
   </si>
   <si>
-    <t xml:space="preserve">Piero Gris</t>
+    <t xml:space="preserve">PIERO GRIS</t>
   </si>
   <si>
     <t xml:space="preserve">PIERO GRIS  (1).jpg</t>
@@ -146,7 +149,7 @@
     <t xml:space="preserve">p005</t>
   </si>
   <si>
-    <t xml:space="preserve">Pellegrini</t>
+    <t xml:space="preserve">PELLEGRINI</t>
   </si>
   <si>
     <t xml:space="preserve">PELLEGRINI  (1).jpg</t>
@@ -161,13 +164,13 @@
     <t xml:space="preserve">p006</t>
   </si>
   <si>
-    <t xml:space="preserve">Slate Gris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rugoso</t>
+    <t xml:space="preserve">SLATE GRIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUGOSO</t>
   </si>
   <si>
     <t xml:space="preserve">SLATE GRIS  (1).jpg</t>
@@ -182,13 +185,13 @@
     <t xml:space="preserve">p007</t>
   </si>
   <si>
-    <t xml:space="preserve">Concret Pulido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66x66 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulido</t>
+    <t xml:space="preserve">CONCRET  PULIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66X66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULIDO</t>
   </si>
   <si>
     <t xml:space="preserve">Interior</t>
@@ -206,7 +209,7 @@
     <t xml:space="preserve">p008</t>
   </si>
   <si>
-    <t xml:space="preserve">Doha Plus Pulido</t>
+    <t xml:space="preserve">DOHA PLUS PULIDO</t>
   </si>
   <si>
     <t xml:space="preserve">DOHA PLUS PULIDO  (1).jpg</t>
@@ -221,106 +224,103 @@
     <t xml:space="preserve">p009</t>
   </si>
   <si>
-    <t xml:space="preserve">Vision Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58x118 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VISION GRAY (1).jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VISION GRAY (2).jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VISION GRAY (3).jpg</t>
+    <t xml:space="preserve">VISION GRAY PLUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58X118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10mm espesor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VISION GRAY PLUS (1).jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VISION GRAY PLUS (2).jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VISION GRAY PLUS (3).jpg</t>
   </si>
   <si>
     <t xml:space="preserve">p010</t>
   </si>
   <si>
-    <t xml:space="preserve">Mahal Off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58x119 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAHAL OFF (1).jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAHAL OFF (2).jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAHAL OFF (3).jpg</t>
+    <t xml:space="preserve">MAHAL OFF PLUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAHAL OFF PLUS (1).jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAHAL OFF PLUS (2).jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAHAL OFF PLUS (3).jpg</t>
   </si>
   <si>
     <t xml:space="preserve">p011</t>
   </si>
   <si>
-    <t xml:space="preserve">Olimpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58x120 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIMPO  (1).jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIMPO  (2).jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIMPO  (3).jpg</t>
+    <t xml:space="preserve">OLIMPO PLUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIMPO PLUS (1).jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIMPO PLUS (2).jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIMPO PLUS (3).jpg</t>
   </si>
   <si>
     <t xml:space="preserve">CÓMO COMPLETAR ESTA PLANILLA</t>
   </si>
   <si>
-    <t xml:space="preserve">Las 11 filas en VERDE ya están cargadas en el sitio de prueba — son las que mandaste. Seguí completando desde la fila 13 en adelante.</t>
+    <t xml:space="preserve">Las filas en VERDE ya están cargadas en el sitio real (alfagate.com.ar). Seguí completando desde la primera fila en blanco.</t>
   </si>
   <si>
     <t xml:space="preserve">COLUMNA POR COLUMNA:</t>
   </si>
   <si>
-    <t xml:space="preserve">id → un código único por producto, ej: p012, p013... (no repetir).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">categoria → EXACTAMENTE una de estas tres palabras (minúscula, sin tildes): pisos-ceramicos / revestimientos / flotantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subcategoria → SOLO para 'pisos-ceramicos': 'Porcelanatos' o 'Gres Ceramicos'. Para revestimientos y flotantes, vacío.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nombre → nombre comercial del producto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tipología → el estilo/material por el que se va a poder filtrar en el sitio (ej: Concreto, Carrara, Plano, Laja). Usá el mismo texto en productos que quieras agrupar juntos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formato → medida, ej: '68x68 cm'.</t>
+    <t xml:space="preserve">id → código único, ej: p012, p013... (no repetir).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">categoria → EXACTAMENTE: pisos-ceramicos / revestimientos / flotantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subcategoria → SOLO para pisos-ceramicos: 'Porcelanatos' o 'Gres Ceramicos'. Vacío para el resto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nombre → nombre comercial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipología → estilo/material para el filtro 'Estilo' del sitio (ej: Concreto, Carrara, Plano, Laja).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formato → medida, para el filtro 'Medida' del sitio (ej: 68X68). Usá el MISMO texto exacto en productos que compartan medida.</t>
   </si>
   <si>
     <t xml:space="preserve">terminacion → ej: Satinado, Pulido, Rugoso.</t>
   </si>
   <si>
-    <t xml:space="preserve">uso → ej: Interior, Interior / Exterior.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">especificaciones → hasta 5 frases cortas separadas por  |  (barra vertical). Recomendado completar, aunque no es obligatorio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foto1, foto2, foto3 → nombre EXACTO del archivo que vas a subir a images/productos (mayúsculas, espacios y paréntesis cuentan letra por letra).</t>
+    <t xml:space="preserve">uso → ej: Interior, Interior- Exterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">especificaciones → hasta 5 datos cortos separados por | (ej: 8,5mm espesor | PEI4 | Antideslizante).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foto1, foto2, foto3 → nombre EXACTO del archivo (mayúsculas, espacios y paréntesis cuentan letra por letra).</t>
   </si>
   <si>
     <t xml:space="preserve">AL TERMINAR CADA TANDA:</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Archivo &gt; Guardar como &gt; CSV (delimitado por comas) (*.csv), nombralo products.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Subilo a GitHub reemplazando el actual (Add file &gt; Upload files).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Subí las fotos correspondientes a images/productos con el nombre exacto de las columnas foto1/foto2/foto3.</t>
+    <t xml:space="preserve">1. Archivo &gt; Guardar como &gt; CSV (delimitado por comas), nombralo products.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Subilo a GitHub reemplazando el actual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Subí las fotos a images/productos con el nombre exacto de foto1/foto2/foto3 (podés seleccionar varias juntas al arrastrar).</t>
   </si>
 </sst>
 </file>
@@ -729,12 +729,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -800,20 +800,22 @@
       <c r="H2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
@@ -822,10 +824,10 @@
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>17</v>
@@ -836,20 +838,22 @@
       <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
@@ -858,10 +862,10 @@
         <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>17</v>
@@ -872,20 +876,22 @@
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
@@ -894,10 +900,10 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>17</v>
@@ -908,20 +914,22 @@
       <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
@@ -930,10 +938,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>17</v>
@@ -944,20 +952,22 @@
       <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -966,34 +976,36 @@
         <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>13</v>
@@ -1002,34 +1014,36 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>13</v>
@@ -1038,34 +1052,36 @@
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>13</v>
@@ -1074,13 +1090,13 @@
         <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>18</v>
@@ -1088,20 +1104,22 @@
       <c r="H10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="J10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>13</v>
@@ -1110,13 +1128,13 @@
         <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>18</v>
@@ -1124,20 +1142,22 @@
       <c r="H11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="J11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>13</v>
@@ -1146,13 +1166,13 @@
         <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>18</v>
@@ -1160,7 +1180,9 @@
       <c r="H12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="J12" s="2" t="s">
         <v>80</v>
       </c>
@@ -1919,12 +1941,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>88</v>
       </c>
@@ -1934,12 +1956,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>91</v>
       </c>
@@ -1954,12 +1976,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>95</v>
       </c>
@@ -1982,7 +2004,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>99</v>
       </c>
